--- a/data-manipulation-scripts/sheets-cleanup/sheets/CAPA ESTICADOR.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/CAPA ESTICADOR.xlsx
@@ -31,7 +31,7 @@
     <t xml:space="preserve"> </t>
   </si>
   <si>
-    <t xml:space="preserve">CAPA ESTICADOR CORRENTE IRON BROS NXR125 150 160 196603 </t>
+    <t xml:space="preserve"> ESTICADOR CORRENTE IRON BROS NXR125 150 160 196603 </t>
   </si>
 </sst>
 </file>
@@ -337,8 +337,12 @@
       <c r="B2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
+      <c r="C2" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D2" s="2">
+        <v>20.0</v>
+      </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3">
